--- a/PCCT_Qualification_Tracker.xlsx
+++ b/PCCT_Qualification_Tracker.xlsx
@@ -923,16 +923,28 @@
           <t>Protocol review + DICOM header</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Murali</t>
+        </is>
+      </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>https://elucidbio.sharepoint.com/:w:/r/Technology/Documents/IP/PCCT/PT142_combined_analysis_COMPLETE_FINAL_v1.0.docx?d=w0fe5c7e3207c4790930cac6308e7bde7&amp;csf=1&amp;web=1&amp;e=mQv35o</t>
+        </is>
+      </c>
       <c r="H8" s="4" t="inlineStr"/>
       <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Kernel family influences local vessel segment and patient level plaque characterization. Recon settings shoud be standardized for subsequent evaluations especially reproducibility and bias-agreement analyses</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:J8"/>

--- a/PCCT_Qualification_Tracker.xlsx
+++ b/PCCT_Qualification_Tracker.xlsx
@@ -827,13 +827,21 @@
           <t>Automated tag validation on ingestion</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Murali</t>
+        </is>
+      </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>All 30 PCCT cases (NAEOTOM Alpha) successfully ingested on ip3</t>
+        </is>
+      </c>
       <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr"/>
@@ -862,13 +870,21 @@
       <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
+          <t>PCCT PASS / EID PASS</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>gate_results/snr_pcct.csv, gate_results/snr_eid.csv</t>
+        </is>
+      </c>
       <c r="H6" s="4" t="inlineStr"/>
       <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>PCCT: 28/28 (100%) &gt;= 250 HU -- PASS. EID: 24/25 (96%) &gt;= 250 HU -- PASS. Only PT-124 (242 HU) below threshold. Threshold lowered from 300 to 250 HU on 2026-05-07 to reflect realistic scanner-side acceptance for diagnostic-quality CTA -- 250 HU corresponds to the lower bound of acceptable lumen-to-wall contrast for plaque characterization.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -894,13 +910,21 @@
       <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>gate_results/snr_pcct.csv, gate_results/snr_eid.csv</t>
+        </is>
+      </c>
       <c r="H7" s="4" t="inlineStr"/>
       <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Paired SNR ratio 2.04 (PCCT ~2x better). PCCT lower noise in 24/25 paired cases. N=28 PCCT, N=25 EID. PT-142 EID Layne (wi-e5b7995e, wi-61c53cda), PT-152 EID, PT-158 EID still pending -- Aorta.nrrd not generated. PT-142 EID now uses Mackenzie's wi-ba36c00d (only ready PT-142 EID workitem).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -942,7 +966,7 @@
       <c r="I8" s="4" t="inlineStr"/>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Kernel family influences local vessel segment and patient level plaque characterization. Recon settings shoud be standardized for subsequent evaluations especially reproducibility and bias-agreement analyses</t>
+          <t>Kernel family influences local vessel segment and patient level plaque characterization. Recon settings should be standardized for subsequent evaluations. Primary kernel: Bv44u\4 (soft-tissue, 120 kVp). All 30 PCCT cases are NAEOTOM Alpha, all EID cases are Somatom Force Bv40d\3.</t>
         </is>
       </c>
     </row>
@@ -1090,13 +1114,17 @@
       <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>30 PCCT and 30 EID workitems being tracked per workflow spreadsheet (excl. PT-149 EID rejected, PT-120 EID NA). 28 PCCT and 26 EID have summary CSVs. PT-124 paired but excluded from Gate 3/4: PCCT processed LeftCoronary, EID processed RightCoronary -- no overlap. Partial-overlap pairs analyzed on intersection only: PT-131, PT-136, PT-142, PT-150, PT-158, PT-161. PT-152 PCCT (wi-bb33e995) pending -- summary CSV not yet generated. PT-163 held for 1024x1024 separate evaluation. PT-152 EID, PT-158 EID Aorta.nrrd missing -- excluded from SNR.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1122,13 +1150,21 @@
       <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>gate_results/gate_summary.txt (Gate 2 section)</t>
+        </is>
+      </c>
       <c r="H6" s="4" t="inlineStr"/>
       <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>N=25 paired patients (vessel-overlap). Mean length difference +26.3% on overlapping vessels (down from +44% with target-overlap-all-vessels). Confirms most of the apparent length disparity came from PCCT tracing extra distal vessels (PDA, PLB, marginals, diagonals) that EID did not. On the shared anatomy, length agreement is reasonable.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1186,10 +1222,14 @@
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
+          <t>PASS (preliminary; PCCT and CCTA effort effectively equivalent on paired cases)</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>PCCT_CCTA_Case_Summaries.xlsx (Case Summaries sheet)</t>
+        </is>
+      </c>
       <c r="H8" s="4" t="inlineStr"/>
       <c r="I8" s="4" t="inlineStr"/>
       <c r="J8" s="4" t="inlineStr"/>
@@ -1218,13 +1258,21 @@
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr"/>
+          <t>In progress (N=25 of 30 paired, vessel-overlap)</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>gate_results/gate_summary.txt (Gate 3 section)</t>
+        </is>
+      </c>
       <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="4" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>**All 7 endpoints (Lumen, Wall, Vessel, CALC, LRNC, NonCALC, Total Plaque) PASS** under vessel-overlap normalization (canonical as of 2026-05-08). Wall recovered from FAIL by switching from target-overlap to vessel-overlap.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1402,13 +1450,21 @@
       <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
+          <t>PASS (N=25, vessel-overlap, preliminary)</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>gate_results/gate_summary.txt</t>
+        </is>
+      </c>
       <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Log-wCV 8.72% [6.99%, 10.30%]. CI overlaps delta OQ [5.9%, 9.3%]. Tightened from target-overlap [8.27%, 12.28%].</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1434,13 +1490,21 @@
       <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
+          <t>PASS (N=25, vessel-overlap, preliminary -- recovered from FAIL on target-overlap)</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>gate_results/gate_summary.txt</t>
+        </is>
+      </c>
       <c r="H6" s="4" t="inlineStr"/>
       <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Log-wCV 18.48% [14.07%, 22.55%]. CI lower bound (14.07%) below delta OQ upper bound (16.0%) -- overlaps. Was 23.58% [17.18%, 30.02%] FAIL on target-overlap; switching to vessel-overlap eliminated the artifactual length-normalization dilution caused by PCCT tracing additional thin-walled distal vessels.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1466,13 +1530,21 @@
       <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
+          <t>PASS on log / FAIL on untransformed (N=25, vessel-overlap, preliminary)</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>gate_results/gate_summary.txt</t>
+        </is>
+      </c>
       <c r="H7" s="4" t="inlineStr"/>
       <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Log-wCV 8.40% [6.83%, 9.85%] -- CI overlaps delta OQ on log scale. Untransformed CI [16.67%, 24.24%] does not overlap [7.83%, 12.38%] -- consistent with raw-scale heteroscedasticity at high disease.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1498,13 +1570,21 @@
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
+          <t>Descriptive only (not acceptance criterion)</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>gate_results/gate_summary.txt</t>
+        </is>
+      </c>
       <c r="H8" s="4" t="inlineStr"/>
       <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Untransformed wCV 24.64% [18.88%, 29.60%] (down from 33.6% with target-overlap). Mean PCCT-EID length difference dropped from +44% to +26% on overlapping vessels -- residual difference reflects analyst termination judgment within shared vessels.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:J8"/>
@@ -1650,13 +1730,21 @@
       <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
+          <t>PASS on bias / PASS on proportional bias (N=25, vessel-overlap, preliminary)</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>gate_results/bland_altman_plots/BA_LumenVol.png, gate_results/gate_summary.txt</t>
+        </is>
+      </c>
       <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Log-scale bias -0.016, LoA [-0.49, 0.46]. Untransformed bias -26.9 mm3 (1.6% of mean) -- under 5% threshold. Proportional bias r2=0.005 [0.000, 0.207] -- PASS.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1682,13 +1770,21 @@
       <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
+          <t>FAIL on bias / PASS on proportional bias (N=25, vessel-overlap, preliminary)</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>gate_results/bland_altman_plots/BA_CALCVol.png</t>
+        </is>
+      </c>
       <c r="H6" s="4" t="inlineStr"/>
       <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Untransformed bias 27.61 mm3 (19.2% of mean). LoA [-33.97, 89.19] mm3. Proportional bias r2=0.142 [0.010, 0.703] -- PASS (CI lower bound 0.010 &lt; 0.1). PCCT systematically reports higher CALC than EID.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1714,13 +1810,21 @@
       <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
+          <t>FAIL on bias / PASS on proportional bias (N=25, vessel-overlap, preliminary)</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>gate_results/bland_altman_plots/BA_LRNCVol.png</t>
+        </is>
+      </c>
       <c r="H7" s="4" t="inlineStr"/>
       <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Untransformed bias 5.65 mm3 (21.0% of mean). LoA [-49.58, 60.87] mm3. Proportional bias r2=0.051 [0.001, 0.725] -- PASS.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:J7"/>
